--- a/_900_CommonText.xlsx
+++ b/_900_CommonText.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4F7789-1A03-4106-8C5E-D09490BF9F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E25243-92A2-454B-AFA0-5D0C2C81D010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="202">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1055,6 +1055,66 @@
   </si>
   <si>
     <t>UID. {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출현 정보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nemy Encounters</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出現情報</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rewards</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>報酬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>入場</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이지 선택</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage Select</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ステ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ージ選択</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2457,10 +2517,62 @@
         <v>189</v>
       </c>
     </row>
-    <row r="71" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="72" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="73" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="74" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="71" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A71" s="3">
+        <v>9000068</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A72" s="2">
+        <v>9000069</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A73" s="3">
+        <v>9000070</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.6">
+      <c r="A74" s="2">
+        <v>9000071</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
     <row r="75" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
     <row r="76" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
     <row r="77" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
